--- a/excel/family-import-DEMO-validations.xlsx
+++ b/excel/family-import-DEMO-validations.xlsx
@@ -22,102 +22,6 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="G2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <rFont val="Calibri"/>
-            <b val="false"/>
-            <i val="false"/>
-            <strike val="false"/>
-            <color rgb="FF000000"/>
-            <sz val="11"/>
-            <u val="none"/>
-          </rPr>
-          <t xml:space="preserve">Required for the Head of family row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <rFont val="Calibri"/>
-            <b val="false"/>
-            <i val="false"/>
-            <strike val="false"/>
-            <color rgb="FF000000"/>
-            <sz val="11"/>
-            <u val="none"/>
-          </rPr>
-          <t xml:space="preserve">Required for the Head of family row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <rFont val="Calibri"/>
-            <b val="false"/>
-            <i val="false"/>
-            <strike val="false"/>
-            <color rgb="FF000000"/>
-            <sz val="11"/>
-            <u val="none"/>
-          </rPr>
-          <t xml:space="preserve">Required for the Head of family row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <rFont val="Calibri"/>
-            <b val="false"/>
-            <i val="false"/>
-            <strike val="false"/>
-            <color rgb="FF000000"/>
-            <sz val="11"/>
-            <u val="none"/>
-          </rPr>
-          <t xml:space="preserve">Required for the Head of family row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <rFont val="Calibri"/>
-            <b val="false"/>
-            <i val="false"/>
-            <strike val="false"/>
-            <color rgb="FF000000"/>
-            <sz val="11"/>
-            <u val="none"/>
-          </rPr>
-          <t xml:space="preserve">Required for the Head of family row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <rFont val="Calibri"/>
-            <b val="false"/>
-            <i val="false"/>
-            <strike val="false"/>
-            <color rgb="FF000000"/>
-            <sz val="11"/>
-            <u val="none"/>
-          </rPr>
-          <t xml:space="preserve">Required for the Head of family row.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="O2" authorId="0">
       <text>
         <r>
@@ -162,7 +66,7 @@
             <sz val="11"/>
             <u val="none"/>
           </rPr>
-          <t xml:space="preserve">Automatic check — fix any row that is not "OK" before importing. This column is ignored on import.</t>
+          <t xml:space="preserve">Automatic check - fix any row that is not "OK" before importing. This column is ignored on import.</t>
         </r>
       </text>
     </comment>
@@ -176,102 +80,6 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="G2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <rFont val="Calibri"/>
-            <b val="false"/>
-            <i val="false"/>
-            <strike val="false"/>
-            <color rgb="FF000000"/>
-            <sz val="11"/>
-            <u val="none"/>
-          </rPr>
-          <t xml:space="preserve">Required for the Head of family row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <rFont val="Calibri"/>
-            <b val="false"/>
-            <i val="false"/>
-            <strike val="false"/>
-            <color rgb="FF000000"/>
-            <sz val="11"/>
-            <u val="none"/>
-          </rPr>
-          <t xml:space="preserve">Required for the Head of family row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <rFont val="Calibri"/>
-            <b val="false"/>
-            <i val="false"/>
-            <strike val="false"/>
-            <color rgb="FF000000"/>
-            <sz val="11"/>
-            <u val="none"/>
-          </rPr>
-          <t xml:space="preserve">Required for the Head of family row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <rFont val="Calibri"/>
-            <b val="false"/>
-            <i val="false"/>
-            <strike val="false"/>
-            <color rgb="FF000000"/>
-            <sz val="11"/>
-            <u val="none"/>
-          </rPr>
-          <t xml:space="preserve">Required for the Head of family row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <rFont val="Calibri"/>
-            <b val="false"/>
-            <i val="false"/>
-            <strike val="false"/>
-            <color rgb="FF000000"/>
-            <sz val="11"/>
-            <u val="none"/>
-          </rPr>
-          <t xml:space="preserve">Required for the Head of family row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <rFont val="Calibri"/>
-            <b val="false"/>
-            <i val="false"/>
-            <strike val="false"/>
-            <color rgb="FF000000"/>
-            <sz val="11"/>
-            <u val="none"/>
-          </rPr>
-          <t xml:space="preserve">Required for the Head of family row.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="O2" authorId="0">
       <text>
         <r>
@@ -309,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="483">
   <si>
     <t>FAMILY</t>
   </si>
@@ -323,10 +131,10 @@
     <t>ADDRESS</t>
   </si>
   <si>
-    <t>SECTOR (who) — codes</t>
-  </si>
-  <si>
-    <t>SERVICES (programs) — codes</t>
+    <t>SECTOR (who) - codes</t>
+  </si>
+  <si>
+    <t>SERVICES (programs) - codes</t>
   </si>
   <si>
     <t>QR Number *</t>
@@ -347,13 +155,13 @@
     <t>Suffix</t>
   </si>
   <si>
-    <t>Birthday</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>CivilStatus</t>
+    <t>Birthday *</t>
+  </si>
+  <si>
+    <t>Sex *</t>
+  </si>
+  <si>
+    <t>CivilStatus *</t>
   </si>
   <si>
     <t>ContactNumber</t>
@@ -362,1296 +170,1392 @@
     <t>Religion</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Job</t>
+    <t>Education *</t>
+  </si>
+  <si>
+    <t>Job *</t>
+  </si>
+  <si>
+    <t>MonthlyIncome *</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Barangay</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>CHECK</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>9000001</t>
+  </si>
+  <si>
+    <t>9000002</t>
+  </si>
+  <si>
+    <t>9000003</t>
+  </si>
+  <si>
+    <t>9000004</t>
+  </si>
+  <si>
+    <t>9000005</t>
+  </si>
+  <si>
+    <t>9000012</t>
+  </si>
+  <si>
+    <t>9000006</t>
+  </si>
+  <si>
+    <t>ABC123</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>9999999999</t>
+  </si>
+  <si>
+    <t>#REF!</t>
+  </si>
+  <si>
+    <t>=A4</t>
+  </si>
+  <si>
+    <t>9000007</t>
+  </si>
+  <si>
+    <t>9000008</t>
+  </si>
+  <si>
+    <t>9000009</t>
+  </si>
+  <si>
+    <t>9000010</t>
+  </si>
+  <si>
+    <t>9000011</t>
+  </si>
+  <si>
+    <t>01-16-1994</t>
+  </si>
+  <si>
+    <t>03-20-1999</t>
+  </si>
+  <si>
+    <t>03-09-1990</t>
+  </si>
+  <si>
+    <t>04-28-1960</t>
+  </si>
+  <si>
+    <t>07-11-2008</t>
+  </si>
+  <si>
+    <t>09-28-1983</t>
+  </si>
+  <si>
+    <t>02-14-2012</t>
+  </si>
+  <si>
+    <t>06-02-1978</t>
+  </si>
+  <si>
+    <t>01-30-2010</t>
+  </si>
+  <si>
+    <t>11-05-1970</t>
+  </si>
+  <si>
+    <t>12-08-1972</t>
+  </si>
+  <si>
+    <t>04-04-1965</t>
+  </si>
+  <si>
+    <t>09-09-1969</t>
+  </si>
+  <si>
+    <t>31-31-2000</t>
+  </si>
+  <si>
+    <t>01-01-1990</t>
+  </si>
+  <si>
+    <t>02-02-1980</t>
+  </si>
+  <si>
+    <t>05-05-1985</t>
+  </si>
+  <si>
+    <t>05-06-1985</t>
+  </si>
+  <si>
+    <t>05-07-1985</t>
+  </si>
+  <si>
+    <t>05-08-1985</t>
+  </si>
+  <si>
+    <t>05-09-1985</t>
+  </si>
+  <si>
+    <t>05-10-1985</t>
+  </si>
+  <si>
+    <t>01-01-1850</t>
+  </si>
+  <si>
+    <t>03-03-1975</t>
+  </si>
+  <si>
+    <t>08-08-2011</t>
+  </si>
+  <si>
+    <t>07-07-1968</t>
+  </si>
+  <si>
+    <t>10-10-1982</t>
+  </si>
+  <si>
+    <t>09-09-2009</t>
+  </si>
+  <si>
+    <t>06-06-1971</t>
+  </si>
+  <si>
+    <t>04-04-2013</t>
+  </si>
+  <si>
+    <t>09732227425</t>
+  </si>
+  <si>
+    <t>09171112222</t>
+  </si>
+  <si>
+    <t>09171234567</t>
+  </si>
+  <si>
+    <t>09129375782</t>
+  </si>
+  <si>
+    <t>09979950257</t>
+  </si>
+  <si>
+    <t>09171230000</t>
+  </si>
+  <si>
+    <t>09181234567</t>
+  </si>
+  <si>
+    <t>09182223333</t>
+  </si>
+  <si>
+    <t>09171234000</t>
+  </si>
+  <si>
+    <t>09171235555</t>
+  </si>
+  <si>
+    <t>12345</t>
+  </si>
+  <si>
+    <t>09171236666</t>
+  </si>
+  <si>
+    <t>09171237777</t>
+  </si>
+  <si>
+    <t>09171238888</t>
+  </si>
+  <si>
+    <t>09171239999</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>Ang</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Roman Catholic</t>
+  </si>
+  <si>
+    <t>UG</t>
+  </si>
+  <si>
+    <t>Private Employee</t>
+  </si>
+  <si>
+    <t>65000</t>
+  </si>
+  <si>
+    <t>844 P. Burgos St.</t>
+  </si>
+  <si>
+    <t>Casile</t>
+  </si>
+  <si>
+    <t>Child</t>
+  </si>
+  <si>
+    <t>Spouse</t>
+  </si>
+  <si>
+    <t>Espino</t>
+  </si>
+  <si>
+    <t>Reyes</t>
+  </si>
+  <si>
+    <t>Ramos</t>
+  </si>
+  <si>
+    <t>Buenaventura</t>
+  </si>
+  <si>
+    <t>Andrada</t>
+  </si>
+  <si>
+    <t>Dela Cruz</t>
+  </si>
+  <si>
+    <t>Torres</t>
+  </si>
+  <si>
+    <t>Aquino</t>
+  </si>
+  <si>
+    <t>Bautista</t>
+  </si>
+  <si>
+    <t>Villanueva</t>
+  </si>
+  <si>
+    <t>Mercado</t>
+  </si>
+  <si>
+    <t>Blanco</t>
+  </si>
+  <si>
+    <t>Letras</t>
+  </si>
+  <si>
+    <t>Zero</t>
+  </si>
+  <si>
+    <t>Grande</t>
+  </si>
+  <si>
+    <t>Erroro</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Ocampo</t>
+  </si>
+  <si>
+    <t>Navarro</t>
+  </si>
+  <si>
+    <t>Salazar</t>
+  </si>
+  <si>
+    <t>Padilla</t>
+  </si>
+  <si>
+    <t>Gutierrez</t>
+  </si>
+  <si>
+    <t>Ramon</t>
+  </si>
+  <si>
+    <t>Carmela</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>Nico</t>
+  </si>
+  <si>
+    <t>Ronald</t>
+  </si>
+  <si>
+    <t>Liza</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Ben</t>
+  </si>
+  <si>
+    <t>Cora</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>Andres</t>
+  </si>
+  <si>
+    <t>NoLastname</t>
+  </si>
+  <si>
+    <t>Juanitolongfirstnamethatgoesonandonandonandonandonandonandonandonandonandonandonandonandonandonandonandon</t>
+  </si>
+  <si>
+    <t>Nilo</t>
+  </si>
+  <si>
+    <t>Rico</t>
+  </si>
+  <si>
+    <t>Zeno</t>
+  </si>
+  <si>
+    <t>Maxi</t>
+  </si>
+  <si>
+    <t>Rene</t>
+  </si>
+  <si>
+    <t>Fely</t>
+  </si>
+  <si>
+    <t>Ignacio</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Efren</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>Toni</t>
+  </si>
+  <si>
+    <t>Noel</t>
+  </si>
+  <si>
+    <t>Rey</t>
+  </si>
+  <si>
+    <t>Tan</t>
+  </si>
+  <si>
+    <t>Lim</t>
+  </si>
+  <si>
+    <t>Malabanan</t>
+  </si>
+  <si>
+    <t>Panganiban</t>
+  </si>
+  <si>
+    <t>Sy</t>
+  </si>
+  <si>
+    <t>Cruz</t>
+  </si>
+  <si>
+    <t>Uy</t>
+  </si>
+  <si>
+    <t>Roque</t>
+  </si>
+  <si>
+    <t>Diaz</t>
+  </si>
+  <si>
+    <t>Lopez</t>
+  </si>
+  <si>
+    <t>Go</t>
+  </si>
+  <si>
+    <t>Yu</t>
+  </si>
+  <si>
+    <t>Junior</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Malee</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Iglesia ni Cristo</t>
+  </si>
+  <si>
+    <t>HS</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>Self-employed</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Retired</t>
+  </si>
+  <si>
+    <t>Construction Worker</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>Farmer</t>
+  </si>
+  <si>
+    <t>Janitor</t>
+  </si>
+  <si>
+    <t>Mechanic</t>
+  </si>
+  <si>
+    <t>Teacher</t>
+  </si>
+  <si>
+    <t>Welder</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>7000</t>
+  </si>
+  <si>
+    <t>plenty</t>
+  </si>
+  <si>
+    <t>12000</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>16000</t>
+  </si>
+  <si>
+    <t>713 Aguinaldo Ave.</t>
+  </si>
+  <si>
+    <t>12 Mabini St.</t>
+  </si>
+  <si>
+    <t>59 Magsaysay St.</t>
+  </si>
+  <si>
+    <t>675 Narra St.</t>
+  </si>
+  <si>
+    <t>88 Rizal Ave.</t>
+  </si>
+  <si>
+    <t>5 Bonifacio St.</t>
+  </si>
+  <si>
+    <t>1 Acacia St.</t>
+  </si>
+  <si>
+    <t>99 Ipil St.</t>
+  </si>
+  <si>
+    <t>77 Sampaguita St.</t>
+  </si>
+  <si>
+    <t>100 Test St.</t>
+  </si>
+  <si>
+    <t>3 Ilang-Ilang St.</t>
+  </si>
+  <si>
+    <t>4 Narra St.</t>
+  </si>
+  <si>
+    <t>5 Narra St.</t>
+  </si>
+  <si>
+    <t>6 Narra St.</t>
+  </si>
+  <si>
+    <t>7 Narra St.</t>
+  </si>
+  <si>
+    <t>8 Narra St.</t>
+  </si>
+  <si>
+    <t>9 Narra St.</t>
+  </si>
+  <si>
+    <t>10 Kalachuchi St.</t>
+  </si>
+  <si>
+    <t>21 Molave St.</t>
+  </si>
+  <si>
+    <t>30 Mahogany St.</t>
+  </si>
+  <si>
+    <t>40 Kamagong St.</t>
+  </si>
+  <si>
+    <t>50 Balete St.</t>
+  </si>
+  <si>
+    <t>Canlalay</t>
+  </si>
+  <si>
+    <t>Poblacion</t>
+  </si>
+  <si>
+    <t>Malamig</t>
+  </si>
+  <si>
+    <t>Loma</t>
+  </si>
+  <si>
+    <t>Malaban</t>
+  </si>
+  <si>
+    <t>Timbao</t>
+  </si>
+  <si>
+    <t>De La Paz</t>
+  </si>
+  <si>
+    <t>Zapote</t>
+  </si>
+  <si>
+    <t>Sto. Domingo</t>
+  </si>
+  <si>
+    <t>Barangay Wakanda</t>
+  </si>
+  <si>
+    <t>Langkiwa</t>
+  </si>
+  <si>
+    <t>Soro-Soro</t>
+  </si>
+  <si>
+    <t>Tubigan</t>
+  </si>
+  <si>
+    <t>ZZZ</t>
+  </si>
+  <si>
+    <t>Relationships</t>
+  </si>
+  <si>
+    <t>SPOUSE</t>
+  </si>
+  <si>
+    <t>CHILD</t>
+  </si>
+  <si>
+    <t>PARENT</t>
+  </si>
+  <si>
+    <t>SIBLING</t>
+  </si>
+  <si>
+    <t>GRANDPARENT</t>
+  </si>
+  <si>
+    <t>GRANDCHILD</t>
+  </si>
+  <si>
+    <t>IN-LAW</t>
+  </si>
+  <si>
+    <t>RELATIVE</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>Suffixes</t>
+  </si>
+  <si>
+    <t>JR</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Sexes</t>
+  </si>
+  <si>
+    <t>MALE</t>
+  </si>
+  <si>
+    <t>FEMALE</t>
+  </si>
+  <si>
+    <t>CivilStatus (code - name)</t>
+  </si>
+  <si>
+    <t>S - SINGLE</t>
+  </si>
+  <si>
+    <t>M - MARRIED</t>
+  </si>
+  <si>
+    <t>W - WIDOW / WIDOWER</t>
+  </si>
+  <si>
+    <t>H - SEPARATED</t>
+  </si>
+  <si>
+    <t>N - LIVE-IN / NOT MARRIED</t>
+  </si>
+  <si>
+    <t>OTHERS</t>
+  </si>
+  <si>
+    <t>Religions</t>
+  </si>
+  <si>
+    <t>ROMAN CATHOLIC</t>
+  </si>
+  <si>
+    <t>IGLESIA NI CRISTO</t>
+  </si>
+  <si>
+    <t>ISLAM</t>
+  </si>
+  <si>
+    <t>BORN AGAIN CHRISTIAN</t>
+  </si>
+  <si>
+    <t>PROTESTANT</t>
+  </si>
+  <si>
+    <t>SEVENTH-DAY ADVENTIST</t>
+  </si>
+  <si>
+    <t>IGLESIA FILIPINA INDEPENDIENTE</t>
+  </si>
+  <si>
+    <t>BIBLE BAPTIST</t>
+  </si>
+  <si>
+    <t>JEHOVAH'S WITNESS</t>
+  </si>
+  <si>
+    <t>CHURCH OF CHRIST</t>
+  </si>
+  <si>
+    <t>INDIGENOUS BELIEFS</t>
+  </si>
+  <si>
+    <t>NO RELIGION</t>
+  </si>
+  <si>
+    <t>Education (code - name)</t>
+  </si>
+  <si>
+    <t>E - ELEMENTARY</t>
+  </si>
+  <si>
+    <t>HS - HIGH SCHOOL</t>
+  </si>
+  <si>
+    <t>UG - UNDERGRADUATE</t>
+  </si>
+  <si>
+    <t>Voc - VOCATIONAL</t>
+  </si>
+  <si>
+    <t>CG - COLLEGE GRADUATE</t>
+  </si>
+  <si>
+    <t>PG - POST GRADUATE</t>
+  </si>
+  <si>
+    <t>Jobs</t>
+  </si>
+  <si>
+    <t>UNEMPLOYED</t>
+  </si>
+  <si>
+    <t>STUDENT</t>
+  </si>
+  <si>
+    <t>HOMEMAKER</t>
+  </si>
+  <si>
+    <t>SELF-EMPLOYED</t>
+  </si>
+  <si>
+    <t>VENDOR</t>
+  </si>
+  <si>
+    <t>DRIVER</t>
+  </si>
+  <si>
+    <t>CONSTRUCTION WORKER</t>
+  </si>
+  <si>
+    <t>FACTORY WORKER</t>
+  </si>
+  <si>
+    <t>OFFICE STAFF</t>
+  </si>
+  <si>
+    <t>TEACHER</t>
+  </si>
+  <si>
+    <t>HEALTHCARE WORKER</t>
+  </si>
+  <si>
+    <t>GOVERNMENT EMPLOYEE</t>
+  </si>
+  <si>
+    <t>PRIVATE EMPLOYEE</t>
+  </si>
+  <si>
+    <t>OFW</t>
+  </si>
+  <si>
+    <t>RETIRED</t>
   </si>
   <si>
     <t>MonthlyIncome</t>
   </si>
   <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Barangay</t>
-  </si>
-  <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>Services</t>
-  </si>
-  <si>
-    <t>CHECK</t>
-  </si>
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>9000001</t>
-  </si>
-  <si>
-    <t>9000002</t>
-  </si>
-  <si>
-    <t>9000003</t>
-  </si>
-  <si>
-    <t>9000004</t>
-  </si>
-  <si>
-    <t>9000005</t>
-  </si>
-  <si>
-    <t>9000006</t>
-  </si>
-  <si>
-    <t>ABC123</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>9999999999</t>
-  </si>
-  <si>
-    <t>#REF!</t>
-  </si>
-  <si>
-    <t>=A4</t>
-  </si>
-  <si>
-    <t>9000007</t>
-  </si>
-  <si>
-    <t>9000008</t>
-  </si>
-  <si>
-    <t>9000009</t>
-  </si>
-  <si>
-    <t>9000010</t>
-  </si>
-  <si>
-    <t>9000011</t>
-  </si>
-  <si>
-    <t>01-16-1994</t>
-  </si>
-  <si>
-    <t>03-20-1999</t>
-  </si>
-  <si>
-    <t>03-09-1990</t>
-  </si>
-  <si>
-    <t>04-28-1960</t>
-  </si>
-  <si>
-    <t>07-11-2008</t>
-  </si>
-  <si>
-    <t>09-28-1983</t>
-  </si>
-  <si>
-    <t>02-14-2012</t>
-  </si>
-  <si>
-    <t>06-02-1978</t>
-  </si>
-  <si>
-    <t>01-30-2010</t>
-  </si>
-  <si>
-    <t>11-05-1970</t>
-  </si>
-  <si>
-    <t>12-08-1972</t>
-  </si>
-  <si>
-    <t>04-04-1965</t>
-  </si>
-  <si>
-    <t>09-09-1969</t>
-  </si>
-  <si>
-    <t>31-31-2000</t>
-  </si>
-  <si>
-    <t>02-02-1980</t>
-  </si>
-  <si>
-    <t>05-05-1985</t>
-  </si>
-  <si>
-    <t>05-06-1985</t>
-  </si>
-  <si>
-    <t>05-07-1985</t>
-  </si>
-  <si>
-    <t>05-08-1985</t>
-  </si>
-  <si>
-    <t>05-09-1985</t>
-  </si>
-  <si>
-    <t>05-10-1985</t>
-  </si>
-  <si>
-    <t>01-01-1850</t>
-  </si>
-  <si>
-    <t>03-03-1975</t>
-  </si>
-  <si>
-    <t>08-08-2011</t>
-  </si>
-  <si>
-    <t>07-07-1968</t>
-  </si>
-  <si>
-    <t>10-10-1982</t>
-  </si>
-  <si>
-    <t>09-09-2009</t>
-  </si>
-  <si>
-    <t>06-06-1971</t>
-  </si>
-  <si>
-    <t>04-04-2013</t>
-  </si>
-  <si>
-    <t>09732227425</t>
-  </si>
-  <si>
-    <t>09171112222</t>
-  </si>
-  <si>
-    <t>09171234567</t>
-  </si>
-  <si>
-    <t>09129375782</t>
-  </si>
-  <si>
-    <t>09979950257</t>
-  </si>
-  <si>
-    <t>09171230000</t>
-  </si>
-  <si>
-    <t>09181234567</t>
-  </si>
-  <si>
-    <t>09182223333</t>
-  </si>
-  <si>
-    <t>09171234000</t>
-  </si>
-  <si>
-    <t>09171235555</t>
-  </si>
-  <si>
-    <t>12345</t>
-  </si>
-  <si>
-    <t>09171236666</t>
-  </si>
-  <si>
-    <t>09171237777</t>
-  </si>
-  <si>
-    <t>09171238888</t>
-  </si>
-  <si>
-    <t>09171239999</t>
-  </si>
-  <si>
-    <t>Head</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
-    <t>Antonio</t>
-  </si>
-  <si>
-    <t>Ang</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Roman Catholic</t>
-  </si>
-  <si>
-    <t>UG</t>
-  </si>
-  <si>
-    <t>Private Employee</t>
-  </si>
-  <si>
-    <t>65000</t>
-  </si>
-  <si>
-    <t>844 P. Burgos St.</t>
-  </si>
-  <si>
-    <t>Casile</t>
-  </si>
-  <si>
-    <t>Child</t>
-  </si>
-  <si>
-    <t>Spouse</t>
-  </si>
-  <si>
-    <t>Espino</t>
-  </si>
-  <si>
-    <t>Reyes</t>
-  </si>
-  <si>
-    <t>Ramos</t>
-  </si>
-  <si>
-    <t>Buenaventura</t>
-  </si>
-  <si>
-    <t>Andrada</t>
-  </si>
-  <si>
-    <t>Dela Peña</t>
-  </si>
-  <si>
-    <t>Torres</t>
-  </si>
-  <si>
-    <t>Aquino</t>
-  </si>
-  <si>
-    <t>Bautista</t>
-  </si>
-  <si>
-    <t>Villanueva</t>
-  </si>
-  <si>
-    <t>Mercado</t>
-  </si>
-  <si>
-    <t>Blanco</t>
-  </si>
-  <si>
-    <t>Letras</t>
-  </si>
-  <si>
-    <t>Zero</t>
-  </si>
-  <si>
-    <t>Grande</t>
-  </si>
-  <si>
-    <t>Erroro</t>
-  </si>
-  <si>
-    <t>Formula</t>
-  </si>
-  <si>
-    <t>Ocampo</t>
-  </si>
-  <si>
-    <t>Navarro</t>
-  </si>
-  <si>
-    <t>Salazar</t>
-  </si>
-  <si>
-    <t>Padilla</t>
-  </si>
-  <si>
-    <t>Gutierrez</t>
-  </si>
-  <si>
-    <t>Ramon</t>
-  </si>
-  <si>
-    <t>Carmela</t>
-  </si>
-  <si>
-    <t>Rafael</t>
-  </si>
-  <si>
-    <t>Nico</t>
-  </si>
-  <si>
-    <t>Ronald</t>
-  </si>
-  <si>
-    <t>Liza</t>
-  </si>
-  <si>
-    <t>Rosa</t>
-  </si>
-  <si>
-    <t>Mark</t>
-  </si>
-  <si>
-    <t>Ben</t>
-  </si>
-  <si>
-    <t>Cora</t>
-  </si>
-  <si>
-    <t>Pedro</t>
-  </si>
-  <si>
-    <t>Elena</t>
-  </si>
-  <si>
-    <t>Andres</t>
-  </si>
-  <si>
-    <t>Juanitolongfirstnamethatgoesonandonandonandonandonandonandonandonandonandonandonandonandonandonandonandon</t>
-  </si>
-  <si>
-    <t>Nilo</t>
-  </si>
-  <si>
-    <t>Rico</t>
-  </si>
-  <si>
-    <t>Zeno</t>
-  </si>
-  <si>
-    <t>Maxi</t>
-  </si>
-  <si>
-    <t>Rene</t>
-  </si>
-  <si>
-    <t>Fely</t>
-  </si>
-  <si>
-    <t>Ignacio</t>
-  </si>
-  <si>
-    <t>Luis</t>
-  </si>
-  <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t>Efren</t>
-  </si>
-  <si>
-    <t>Grace</t>
-  </si>
-  <si>
-    <t>Toni</t>
-  </si>
-  <si>
-    <t>Noel</t>
-  </si>
-  <si>
-    <t>Rey</t>
-  </si>
-  <si>
-    <t>Tan</t>
-  </si>
-  <si>
-    <t>Lim</t>
-  </si>
-  <si>
-    <t>Malabanan</t>
-  </si>
-  <si>
-    <t>Panganiban</t>
-  </si>
-  <si>
-    <t>Sy</t>
-  </si>
-  <si>
-    <t>Cruz</t>
-  </si>
-  <si>
-    <t>Uy</t>
-  </si>
-  <si>
-    <t>Roque</t>
-  </si>
-  <si>
-    <t>Diaz</t>
-  </si>
-  <si>
-    <t>Lopez</t>
-  </si>
-  <si>
-    <t>Go</t>
-  </si>
-  <si>
-    <t>Yu</t>
-  </si>
-  <si>
-    <t>Junior</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Malee</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>Iglesia ni Cristo</t>
-  </si>
-  <si>
-    <t>HS</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>CG</t>
-  </si>
-  <si>
-    <t>Self-employed</t>
-  </si>
-  <si>
-    <t>Vendor</t>
-  </si>
-  <si>
-    <t>Retired</t>
-  </si>
-  <si>
-    <t>Construction Worker</t>
-  </si>
-  <si>
-    <t>Driver</t>
-  </si>
-  <si>
-    <t>Farmer</t>
-  </si>
-  <si>
-    <t>Janitor</t>
-  </si>
-  <si>
-    <t>Mechanic</t>
-  </si>
-  <si>
-    <t>Teacher</t>
-  </si>
-  <si>
-    <t>Welder</t>
-  </si>
-  <si>
-    <t>40000</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>8000</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>15000</t>
-  </si>
-  <si>
-    <t>7000</t>
-  </si>
-  <si>
-    <t>plenty</t>
-  </si>
-  <si>
-    <t>12000</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>16000</t>
-  </si>
-  <si>
-    <t>713 Aguinaldo Ave.</t>
-  </si>
-  <si>
-    <t>12 Mabini St.</t>
-  </si>
-  <si>
-    <t>59 Magsaysay St.</t>
-  </si>
-  <si>
-    <t>675 Narra St.</t>
-  </si>
-  <si>
-    <t>88 Rizal Ave.</t>
-  </si>
-  <si>
-    <t>5 Bonifacio St.</t>
-  </si>
-  <si>
-    <t>1 Acacia St.</t>
-  </si>
-  <si>
-    <t>99 Ipil St.</t>
-  </si>
-  <si>
-    <t>77 Sampaguita St.</t>
-  </si>
-  <si>
-    <t>3 Ilang-Ilang St.</t>
-  </si>
-  <si>
-    <t>4 Narra St.</t>
-  </si>
-  <si>
-    <t>5 Narra St.</t>
-  </si>
-  <si>
-    <t>6 Narra St.</t>
-  </si>
-  <si>
-    <t>7 Narra St.</t>
-  </si>
-  <si>
-    <t>8 Narra St.</t>
-  </si>
-  <si>
-    <t>9 Narra St.</t>
-  </si>
-  <si>
-    <t>10 Kalachuchi St.</t>
-  </si>
-  <si>
-    <t>21 Molave St.</t>
-  </si>
-  <si>
-    <t>30 Mahogany St.</t>
-  </si>
-  <si>
-    <t>40 Kamagong St.</t>
-  </si>
-  <si>
-    <t>50 Balete St.</t>
-  </si>
-  <si>
-    <t>Canlalay</t>
-  </si>
-  <si>
-    <t>Poblacion</t>
-  </si>
-  <si>
-    <t>Malamig</t>
-  </si>
-  <si>
-    <t>Loma</t>
-  </si>
-  <si>
-    <t>Malaban</t>
-  </si>
-  <si>
-    <t>Timbao</t>
-  </si>
-  <si>
-    <t>De La Paz</t>
-  </si>
-  <si>
-    <t>Zapote</t>
-  </si>
-  <si>
-    <t>Sto. Domingo</t>
-  </si>
-  <si>
-    <t>Barangay Wakanda</t>
-  </si>
-  <si>
-    <t>Langkiwa</t>
-  </si>
-  <si>
-    <t>Soro-soro</t>
-  </si>
-  <si>
-    <t>Tubigan</t>
-  </si>
-  <si>
-    <t>ZZZ</t>
-  </si>
-  <si>
-    <t>Relationships</t>
-  </si>
-  <si>
-    <t>Parent</t>
-  </si>
-  <si>
-    <t>Sibling</t>
-  </si>
-  <si>
-    <t>Grandparent</t>
-  </si>
-  <si>
-    <t>Grandchild</t>
-  </si>
-  <si>
-    <t>In-law</t>
-  </si>
-  <si>
-    <t>Relative</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Suffixes</t>
-  </si>
-  <si>
-    <t>Jr</t>
-  </si>
-  <si>
-    <t>Sr</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>III</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Sexes</t>
-  </si>
-  <si>
-    <t>CivilStatus (code - name)</t>
+    <t>NO REGULAR INCOME</t>
+  </si>
+  <si>
+    <t>BELOW PHP 8,000</t>
+  </si>
+  <si>
+    <t>PHP 8,000 - 13,000</t>
+  </si>
+  <si>
+    <t>PHP 13,001 - 18,000</t>
+  </si>
+  <si>
+    <t>PHP 18,001 - 25,000</t>
+  </si>
+  <si>
+    <t>PHP 25,001 - 40,000</t>
+  </si>
+  <si>
+    <t>PHP 40,001 - 65,000</t>
+  </si>
+  <si>
+    <t>PHP 65,001 - 100,000</t>
+  </si>
+  <si>
+    <t>PHP 100,001 - 150,000</t>
+  </si>
+  <si>
+    <t>PHP 150,001 - 250,000</t>
+  </si>
+  <si>
+    <t>ABOVE PHP 250,000</t>
+  </si>
+  <si>
+    <t>Barangays</t>
+  </si>
+  <si>
+    <t>BIÑAN</t>
+  </si>
+  <si>
+    <t>BUNGAHAN</t>
+  </si>
+  <si>
+    <t>CANLALAY</t>
+  </si>
+  <si>
+    <t>CASILE</t>
+  </si>
+  <si>
+    <t>DE LA PAZ</t>
+  </si>
+  <si>
+    <t>GANADO</t>
+  </si>
+  <si>
+    <t>LANGKIWA</t>
+  </si>
+  <si>
+    <t>LOMA</t>
+  </si>
+  <si>
+    <t>MALABAN</t>
+  </si>
+  <si>
+    <t>MALAMIG</t>
+  </si>
+  <si>
+    <t>MAMPLASAN</t>
+  </si>
+  <si>
+    <t>PLATERO</t>
+  </si>
+  <si>
+    <t>POBLACION</t>
+  </si>
+  <si>
+    <t>SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>SAN JOSE</t>
+  </si>
+  <si>
+    <t>SAN VICENTE</t>
+  </si>
+  <si>
+    <t>SANTO DOMINGO</t>
+  </si>
+  <si>
+    <t>SANTO NIÑO</t>
+  </si>
+  <si>
+    <t>SANTO TOMAS</t>
+  </si>
+  <si>
+    <t>SORO-SORO</t>
+  </si>
+  <si>
+    <t>TIMBAO</t>
+  </si>
+  <si>
+    <t>TUBIGAN</t>
+  </si>
+  <si>
+    <t>ZAPOTE</t>
+  </si>
+  <si>
+    <t>Sector code</t>
+  </si>
+  <si>
+    <t>Sector name</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>SENIOR CITIZEN</t>
+  </si>
+  <si>
+    <t>PWD</t>
+  </si>
+  <si>
+    <t>PERSON WITH DISABILITY</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>SOLO PARENT</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>BATA (CHILDREN)</t>
+  </si>
+  <si>
+    <t>LGBT</t>
+  </si>
+  <si>
+    <t>LGBTQIA+</t>
+  </si>
+  <si>
+    <t>OVERSEAS FILIPINO WORKER</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>INDIGENOUS PEOPLE</t>
+  </si>
+  <si>
+    <t>IDP</t>
+  </si>
+  <si>
+    <t>INTERNALLY DISPLACED PERSON</t>
+  </si>
+  <si>
+    <t>PDL</t>
+  </si>
+  <si>
+    <t>PERSONS DEPRIVED OF LIBERTY</t>
+  </si>
+  <si>
+    <t>OTHER SECTORS</t>
+  </si>
+  <si>
+    <t>IW</t>
+  </si>
+  <si>
+    <t>Informal Worker</t>
+  </si>
+  <si>
+    <t>Service code</t>
+  </si>
+  <si>
+    <t>Service name</t>
+  </si>
+  <si>
+    <t>Service category</t>
+  </si>
+  <si>
+    <t>SC1</t>
+  </si>
+  <si>
+    <t>REGISTERED OSCA BIÑAN</t>
+  </si>
+  <si>
+    <t>SC2</t>
+  </si>
+  <si>
+    <t>LOCAL PENSIONER</t>
+  </si>
+  <si>
+    <t>SC3</t>
+  </si>
+  <si>
+    <t>NATIONAL PENSIONER</t>
+  </si>
+  <si>
+    <t>SC4</t>
+  </si>
+  <si>
+    <t>CENTENARIAN LOCAL AWARDEE</t>
+  </si>
+  <si>
+    <t>SC5</t>
+  </si>
+  <si>
+    <t>CENTENARIAN NATIONAL AWARDEE</t>
+  </si>
+  <si>
+    <t>SC6</t>
+  </si>
+  <si>
+    <t>CENTENARIAN PROVINCE AWARDEE</t>
+  </si>
+  <si>
+    <t>SC7</t>
+  </si>
+  <si>
+    <t>EYEGLASSES ASSISTANCE</t>
+  </si>
+  <si>
+    <t>SC8</t>
+  </si>
+  <si>
+    <t>ONE TIME CASH INCENTIVE (85YRS OLD)</t>
+  </si>
+  <si>
+    <t>SC9</t>
+  </si>
+  <si>
+    <t>WHEELCHAIR / CRUTCHES</t>
+  </si>
+  <si>
+    <t>PWD1</t>
+  </si>
+  <si>
+    <t>REGISTERED PWD IN BIÑAN</t>
+  </si>
+  <si>
+    <t>PWD2</t>
+  </si>
+  <si>
+    <t>BIÑAN CITY DEVELOPMENT CENTER</t>
+  </si>
+  <si>
+    <t>PWD3</t>
+  </si>
+  <si>
+    <t>BIRTHDAY CASH GIFT</t>
+  </si>
+  <si>
+    <t>PWD4</t>
+  </si>
+  <si>
+    <t>PROJECT ARUGA</t>
+  </si>
+  <si>
+    <t>PWD5</t>
+  </si>
+  <si>
+    <t>SUBSIDY FOR UNEMPLOYABLE PWD</t>
+  </si>
+  <si>
+    <t>SP1</t>
+  </si>
+  <si>
+    <t>REGISTERED SOLO PARENT IN BIÑAN</t>
+  </si>
+  <si>
+    <t>SP2</t>
+  </si>
+  <si>
+    <t>MONTHLY SUBSIDY FOR SOLO PARENT</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>BAHAY PAG-ASA</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>ECCD</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>SUPPLEMENTARY FEEDING PROGRAM</t>
+  </si>
+  <si>
+    <t>FA1</t>
+  </si>
+  <si>
+    <t>BALIK PROBINSYA</t>
+  </si>
+  <si>
+    <t>FINANCIAL ASSISTANCE PROGRAMS</t>
+  </si>
+  <si>
+    <t>FA2</t>
+  </si>
+  <si>
+    <t>BURIAL ASSISTANCE</t>
+  </si>
+  <si>
+    <t>FA3</t>
+  </si>
+  <si>
+    <t>DENTAL ASSISTANCE</t>
+  </si>
+  <si>
+    <t>FA4</t>
+  </si>
+  <si>
+    <t>FA5</t>
+  </si>
+  <si>
+    <t>LINGAP SA MAHIRAP</t>
+  </si>
+  <si>
+    <t>FA6</t>
+  </si>
+  <si>
+    <t>MEDICAL ASSISTANCE</t>
+  </si>
+  <si>
+    <t>SWPS1</t>
+  </si>
+  <si>
+    <t>BALAY SILANGAN</t>
+  </si>
+  <si>
+    <t>SOCIAL WELFARE PROGRAMS AND SERVICES</t>
+  </si>
+  <si>
+    <t>SWPS2</t>
+  </si>
+  <si>
+    <t>BUSINESS SKILLS MANAGEMENT TRAINING</t>
+  </si>
+  <si>
+    <t>SWPS3</t>
+  </si>
+  <si>
+    <t>COUNSELING / DIALOGUE</t>
+  </si>
+  <si>
+    <t>SWPS4</t>
+  </si>
+  <si>
+    <t>FAMILY DEVELOPMENT SESSION</t>
+  </si>
+  <si>
+    <t>SWPS5</t>
+  </si>
+  <si>
+    <t>GENDER SENSITIVITY TRAINING</t>
+  </si>
+  <si>
+    <t>SWPS6</t>
+  </si>
+  <si>
+    <t>LEGAL ASSISTANCE / FREE NOTARY</t>
+  </si>
+  <si>
+    <t>SWPS7</t>
+  </si>
+  <si>
+    <t>LICENSED FOSTER PARENT</t>
+  </si>
+  <si>
+    <t>SWPS8</t>
+  </si>
+  <si>
+    <t>PAMASKONG HANDOG</t>
+  </si>
+  <si>
+    <t>SWPS9</t>
+  </si>
+  <si>
+    <t>PARENT EFFECTIVENESS SERVICE</t>
+  </si>
+  <si>
+    <t>SWPS10</t>
+  </si>
+  <si>
+    <t>PMOC (PRE-MARRIAGE ORIENTATION / COUNSELING)</t>
+  </si>
+  <si>
+    <t>SWPS11</t>
+  </si>
+  <si>
+    <t>REFERRAL</t>
+  </si>
+  <si>
+    <t>4PS</t>
+  </si>
+  <si>
+    <t>4PS (PANTAWID PAMILYANG PILIPINO PROGRAMS)</t>
+  </si>
+  <si>
+    <t>EDA1</t>
+  </si>
+  <si>
+    <t>CASH ASSISTANCE</t>
+  </si>
+  <si>
+    <t>EMERGENCY / DISASTER ASSISTANCE PROGRAMS</t>
+  </si>
+  <si>
+    <t>EDA2</t>
+  </si>
+  <si>
+    <t>CASH FOR WORK</t>
+  </si>
+  <si>
+    <t>EDA3</t>
+  </si>
+  <si>
+    <t>EMERGENCY SHELTER (LOCAL)</t>
+  </si>
+  <si>
+    <t>EDA4</t>
+  </si>
+  <si>
+    <t>EMERGENCY SHELTER (NATIONAL / NHA)</t>
+  </si>
+  <si>
+    <t>EDA5</t>
+  </si>
+  <si>
+    <t>EMERGENCY SHELTER (PROVINCE)</t>
+  </si>
+  <si>
+    <t>EDA6</t>
+  </si>
+  <si>
+    <t>FOOD FOR WORK</t>
+  </si>
+  <si>
+    <t>EDA7</t>
+  </si>
+  <si>
+    <t>NON-FOOD ASSISTANCE</t>
+  </si>
+  <si>
+    <t>EDA8</t>
+  </si>
+  <si>
+    <t>RELIEF FOOD PACK</t>
+  </si>
+  <si>
+    <t>EDA9</t>
+  </si>
+  <si>
+    <t>TEMPORARY SHELTER</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>05-14-1958</t>
+  </si>
+  <si>
+    <t>M - Married</t>
+  </si>
+  <si>
+    <t>CG - College Graduate</t>
+  </si>
+  <si>
+    <t>123 Rizal St.</t>
+  </si>
+  <si>
+    <t>SC1, SC2, FA6</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>09-02-1962</t>
+  </si>
+  <si>
+    <t>09170001111</t>
+  </si>
+  <si>
+    <t>HS - High School</t>
+  </si>
+  <si>
+    <t>Homemaker</t>
+  </si>
+  <si>
+    <t>No regular income</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>01-10-2014</t>
   </si>
   <si>
     <t>S - Single</t>
   </si>
   <si>
-    <t>M - Married</t>
-  </si>
-  <si>
-    <t>W - Widow / Widower</t>
-  </si>
-  <si>
-    <t>H - Separated</t>
-  </si>
-  <si>
-    <t>N - Live-in / Not Married</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>Religions</t>
+    <t>E - Elementary</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>B2, B3</t>
+  </si>
+  <si>
+    <t>07-07-1990</t>
   </si>
   <si>
     <t>Islam</t>
   </si>
   <si>
-    <t>Born Again Christian</t>
-  </si>
-  <si>
-    <t>Protestant</t>
-  </si>
-  <si>
-    <t>Seventh-day Adventist</t>
-  </si>
-  <si>
-    <t>Iglesia Filipina Independiente</t>
-  </si>
-  <si>
-    <t>Bible Baptist</t>
-  </si>
-  <si>
-    <t>Jehovah's Witness</t>
-  </si>
-  <si>
-    <t>Church of Christ</t>
-  </si>
-  <si>
-    <t>Indigenous Beliefs</t>
-  </si>
-  <si>
-    <t>No Religion</t>
-  </si>
-  <si>
-    <t>Education (code - name)</t>
-  </si>
-  <si>
-    <t>E - Elementary</t>
-  </si>
-  <si>
-    <t>HS - High School</t>
-  </si>
-  <si>
     <t>UG - Undergraduate</t>
   </si>
   <si>
-    <t>Voc - Vocational</t>
-  </si>
-  <si>
-    <t>CG - College Graduate</t>
-  </si>
-  <si>
-    <t>PG - Post Graduate</t>
-  </si>
-  <si>
-    <t>Jobs</t>
-  </si>
-  <si>
-    <t>Unemployed</t>
-  </si>
-  <si>
-    <t>Student</t>
-  </si>
-  <si>
-    <t>Homemaker</t>
-  </si>
-  <si>
-    <t>Factory Worker</t>
-  </si>
-  <si>
-    <t>Office Staff</t>
-  </si>
-  <si>
-    <t>Healthcare Worker</t>
-  </si>
-  <si>
-    <t>Government Employee</t>
-  </si>
-  <si>
-    <t>OFW</t>
-  </si>
-  <si>
-    <t>No regular income</t>
-  </si>
-  <si>
-    <t>Below PHP 8,000</t>
-  </si>
-  <si>
-    <t>PHP 8,000 - 13,000</t>
-  </si>
-  <si>
-    <t>PHP 13,001 - 18,000</t>
-  </si>
-  <si>
-    <t>PHP 18,001 - 25,000</t>
-  </si>
-  <si>
-    <t>PHP 25,001 - 40,000</t>
-  </si>
-  <si>
-    <t>PHP 40,001 - 65,000</t>
-  </si>
-  <si>
-    <t>PHP 65,001 - 100,000</t>
-  </si>
-  <si>
-    <t>PHP 100,001 - 150,000</t>
-  </si>
-  <si>
-    <t>PHP 150,001 - 250,000</t>
-  </si>
-  <si>
-    <t>Above PHP 250,000</t>
-  </si>
-  <si>
-    <t>Barangays</t>
-  </si>
-  <si>
-    <t>Binan</t>
-  </si>
-  <si>
-    <t>Bungahan</t>
-  </si>
-  <si>
-    <t>Santo Tomas (Calabuso)</t>
-  </si>
-  <si>
-    <t>Ganado</t>
-  </si>
-  <si>
-    <t>San Francisco (Halang)</t>
-  </si>
-  <si>
-    <t>Mamplasan</t>
-  </si>
-  <si>
-    <t>Platero</t>
-  </si>
-  <si>
-    <t>Santo Nino</t>
-  </si>
-  <si>
-    <t>San Antonio</t>
-  </si>
-  <si>
-    <t>San Jose</t>
-  </si>
-  <si>
-    <t>San Vicente</t>
-  </si>
-  <si>
-    <t>Soro-Soro</t>
-  </si>
-  <si>
-    <t>Santo Domingo</t>
-  </si>
-  <si>
-    <t>Sector code</t>
-  </si>
-  <si>
-    <t>Sector name</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>Senior Citizen</t>
-  </si>
-  <si>
-    <t>PWD</t>
-  </si>
-  <si>
-    <t>Person with Disability</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>Solo Parent</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Bata (Children)</t>
-  </si>
-  <si>
-    <t>LGBT</t>
-  </si>
-  <si>
-    <t>LGBTQIA+</t>
-  </si>
-  <si>
-    <t>Overseas Filipino Worker</t>
-  </si>
-  <si>
-    <t>IP</t>
-  </si>
-  <si>
-    <t>Indigenous People</t>
-  </si>
-  <si>
-    <t>IDP</t>
-  </si>
-  <si>
-    <t>Internally Displaced Person</t>
-  </si>
-  <si>
-    <t>PDL</t>
-  </si>
-  <si>
-    <t>Persons Deprived of Liberty</t>
-  </si>
-  <si>
-    <t>OTHER</t>
-  </si>
-  <si>
-    <t>Other Sectors</t>
-  </si>
-  <si>
-    <t>TS</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Service code</t>
-  </si>
-  <si>
-    <t>Service name</t>
-  </si>
-  <si>
-    <t>Service category</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>Bahay Pag-Asa</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>ECCD</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>Supplementary Feeding Program</t>
-  </si>
-  <si>
-    <t>EDA1</t>
-  </si>
-  <si>
-    <t>Cash Assistance</t>
-  </si>
-  <si>
-    <t>Emergency / Disaster Assistance Programs</t>
-  </si>
-  <si>
-    <t>EDA2</t>
-  </si>
-  <si>
-    <t>Cash for Work</t>
-  </si>
-  <si>
-    <t>EDA3</t>
-  </si>
-  <si>
-    <t>Emergency Shelter (Local)</t>
-  </si>
-  <si>
-    <t>EDA4</t>
-  </si>
-  <si>
-    <t>Emergency Shelter (National / NHA)</t>
-  </si>
-  <si>
-    <t>EDA5</t>
-  </si>
-  <si>
-    <t>Emergency Shelter (Province)</t>
-  </si>
-  <si>
-    <t>EDA6</t>
-  </si>
-  <si>
-    <t>Food for Work</t>
-  </si>
-  <si>
-    <t>EDA7</t>
-  </si>
-  <si>
-    <t>Non-Food Assistance</t>
-  </si>
-  <si>
-    <t>EDA8</t>
-  </si>
-  <si>
-    <t>Relief Food Pack</t>
-  </si>
-  <si>
-    <t>EDA9</t>
-  </si>
-  <si>
-    <t>Temporary Shelter</t>
-  </si>
-  <si>
-    <t>FA1</t>
-  </si>
-  <si>
-    <t>Balik Probinsya</t>
-  </si>
-  <si>
-    <t>Financial Assistance Programs</t>
-  </si>
-  <si>
-    <t>FA2</t>
-  </si>
-  <si>
-    <t>Burial Assistance</t>
-  </si>
-  <si>
-    <t>FA3</t>
-  </si>
-  <si>
-    <t>Dental Assistance</t>
-  </si>
-  <si>
-    <t>FA4</t>
-  </si>
-  <si>
-    <t>Eyeglasses Assistance</t>
-  </si>
-  <si>
-    <t>FA5</t>
-  </si>
-  <si>
-    <t>Lingap sa Mahirap</t>
-  </si>
-  <si>
-    <t>FA6</t>
-  </si>
-  <si>
-    <t>Medical Assistance</t>
-  </si>
-  <si>
-    <t>PWD1</t>
-  </si>
-  <si>
-    <t>Registered PWD in Biñan</t>
-  </si>
-  <si>
-    <t>PWD2</t>
-  </si>
-  <si>
-    <t>Biñan City Development Center</t>
-  </si>
-  <si>
-    <t>PWD3</t>
-  </si>
-  <si>
-    <t>Birthday Cash Gift</t>
-  </si>
-  <si>
-    <t>PWD4</t>
-  </si>
-  <si>
-    <t>Project Aruga</t>
-  </si>
-  <si>
-    <t>PWD5</t>
-  </si>
-  <si>
-    <t>Subsidy for Unemployable PWD</t>
-  </si>
-  <si>
-    <t>SC1</t>
-  </si>
-  <si>
-    <t>Registered OSCA Biñan</t>
-  </si>
-  <si>
-    <t>SC2</t>
-  </si>
-  <si>
-    <t>Local Pensioner</t>
-  </si>
-  <si>
-    <t>SC3</t>
-  </si>
-  <si>
-    <t>National Pensioner</t>
-  </si>
-  <si>
-    <t>SC4</t>
-  </si>
-  <si>
-    <t>Centenarian Local Awardee</t>
-  </si>
-  <si>
-    <t>SC5</t>
-  </si>
-  <si>
-    <t>Centenarian National Awardee</t>
-  </si>
-  <si>
-    <t>SC6</t>
-  </si>
-  <si>
-    <t>Centenarian Province Awardee</t>
-  </si>
-  <si>
-    <t>SC7</t>
-  </si>
-  <si>
-    <t>SC8</t>
-  </si>
-  <si>
-    <t>One Time Cash Incentive (85yrs old)</t>
-  </si>
-  <si>
-    <t>SC9</t>
-  </si>
-  <si>
-    <t>Wheelchair / Crutches</t>
-  </si>
-  <si>
-    <t>SWPS1</t>
-  </si>
-  <si>
-    <t>Balay Silangan</t>
-  </si>
-  <si>
-    <t>Social Welfare Programs and Services</t>
-  </si>
-  <si>
-    <t>SWPS2</t>
-  </si>
-  <si>
-    <t>Business Skills Management Training</t>
-  </si>
-  <si>
-    <t>SWPS3</t>
-  </si>
-  <si>
-    <t>Counseling / Dialogue</t>
-  </si>
-  <si>
-    <t>SWPS4</t>
-  </si>
-  <si>
-    <t>Family Development Session</t>
-  </si>
-  <si>
-    <t>SWPS5</t>
-  </si>
-  <si>
-    <t>Gender Sensitivity Training</t>
-  </si>
-  <si>
-    <t>SWPS6</t>
-  </si>
-  <si>
-    <t>Legal Assistance / Free Notary</t>
-  </si>
-  <si>
-    <t>SWPS7</t>
-  </si>
-  <si>
-    <t>Licensed Foster Parent</t>
-  </si>
-  <si>
-    <t>SWPS8</t>
-  </si>
-  <si>
-    <t>Pamaskong Handog</t>
-  </si>
-  <si>
-    <t>SWPS9</t>
-  </si>
-  <si>
-    <t>Parent Effectiveness Service</t>
-  </si>
-  <si>
-    <t>SWPS10</t>
-  </si>
-  <si>
-    <t>PMOC (Pre-Marriage Orientation / Counseling)</t>
-  </si>
-  <si>
-    <t>SWPS11</t>
-  </si>
-  <si>
-    <t>Referral</t>
-  </si>
-  <si>
-    <t>4PS</t>
-  </si>
-  <si>
-    <t>4Ps (Pantawid Pamilyang Pilipino Programs)</t>
-  </si>
-  <si>
-    <t>SP1</t>
-  </si>
-  <si>
-    <t>Registered Solo Parent in Biñan</t>
-  </si>
-  <si>
-    <t>SP2</t>
-  </si>
-  <si>
-    <t>Monthly Subsidy for Solo Parent</t>
-  </si>
-  <si>
-    <t>TS1</t>
-  </si>
-  <si>
-    <t>Test Sector Services</t>
-  </si>
-  <si>
-    <t>TSC1</t>
-  </si>
-  <si>
-    <t>Test Categories services and programs</t>
-  </si>
-  <si>
-    <t>Test Categories</t>
-  </si>
-  <si>
-    <t>Dela Cruz</t>
-  </si>
-  <si>
-    <t>Juan</t>
-  </si>
-  <si>
-    <t>05-14-1958</t>
-  </si>
-  <si>
-    <t>123 Rizal St.</t>
-  </si>
-  <si>
-    <t>SC1, SC2, FA6</t>
-  </si>
-  <si>
-    <t>Maria</t>
-  </si>
-  <si>
-    <t>09-02-1962</t>
-  </si>
-  <si>
-    <t>09170001111</t>
-  </si>
-  <si>
-    <t>Jose</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>01-10-2014</t>
-  </si>
-  <si>
-    <t>B2, B3</t>
-  </si>
-  <si>
-    <t>07-07-1990</t>
-  </si>
-  <si>
     <t>5 Mabini St.</t>
   </si>
   <si>
@@ -1661,7 +1565,7 @@
     <t>PWD1, EDA5, 4PS</t>
   </si>
   <si>
-    <t>Examples only — enter real data on the "Families" sheet. One row per person. Name order is Last Name, First Name, Middle Name. Birthday is MM-DD-YYYY. Mark each head of family with Relationship = Head. Put as many families as you like in one file: each family gets its own QR number, shared by its members. Members leave Address and Barangay blank — they automatically use the head's address. SECTOR = WHO the person is (SC, PWD, SP, B, LGBT, OFW, IP, IDP, PDL, or OTHER) and SERVICES = the programs they RECEIVED (e.g. SC1, FA6, EDA5, 4PS) — both take CODES separated by commas; see the Reference sheet. " * " marks always-required columns; the Head row also needs Birthday, Sex, Civil Status, Education, Job, Monthly Income, Address and Barangay.</t>
+    <t>Examples only - enter real data on the "Families" sheet. One row per person. Name order is Last Name, First Name, Middle Name. Birthday is MM-DD-YYYY. Mark each head of family with Relationship = Head. Put as many families as you like in one file: each family gets its own QR number, shared by its members. Members leave Address and Barangay blank - they automatically use the head's address. SECTOR = WHO the person is (SC, PWD, SP, B, LGBT, OFW, IP, IDP, PDL, or OTHER) and SERVICES = the programs they RECEIVED (e.g. SC1, FA6, EDA5, 4PS) - both take CODES separated by commas; see the Reference sheet. " * " marks columns needed for a COMPLETE record (incl. Birthday, Sex, Civil Status, Education, Job and Monthly Income). Blank cells do not block the import: the row is saved with those fields empty and the family is listed on the Data Completeness report until the data is collected. The Head row also carries the family's Address and Barangay.</t>
   </si>
 </sst>
 </file>
@@ -2314,47 +2218,47 @@
         <v>26</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q3" s="12"/>
       <c r="R3" s="12"/>
@@ -2368,47 +2272,47 @@
         <v>27</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q4" s="12"/>
       <c r="R4" s="12"/>
@@ -2422,47 +2326,47 @@
         <v>28</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="O5" s="12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q5" s="12"/>
       <c r="R5" s="12"/>
@@ -2476,47 +2380,47 @@
         <v>29</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q6" s="12"/>
       <c r="R6" s="12"/>
@@ -2530,23 +2434,23 @@
         <v>30</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="11"/>
@@ -2568,47 +2472,47 @@
         <v>31</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q8" s="12"/>
       <c r="R8" s="12"/>
@@ -2622,23 +2526,23 @@
         <v>31</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I9" s="12"/>
       <c r="J9" s="11"/>
@@ -2660,26 +2564,26 @@
         <v>32</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="12"/>
@@ -2687,10 +2591,10 @@
       <c r="M10" s="12"/>
       <c r="N10" s="12"/>
       <c r="O10" s="12" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
@@ -2704,23 +2608,23 @@
         <v>32</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I11" s="12"/>
       <c r="J11" s="11"/>
@@ -2742,47 +2646,47 @@
         <v>33</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q12" s="12"/>
       <c r="R12" s="12"/>
@@ -2796,45 +2700,45 @@
         <v>33</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J13" s="11"/>
       <c r="K13" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O13" s="12" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
@@ -2848,47 +2752,47 @@
         <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q14" s="12"/>
       <c r="R14" s="12"/>
@@ -2902,47 +2806,47 @@
         <v>34</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="O15" s="12" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q15" s="12"/>
       <c r="R15" s="12"/>
@@ -2956,49 +2860,49 @@
         <v>35</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M16" s="12"/>
       <c r="N16" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q16" s="12"/>
       <c r="R16" s="12" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="S16" t="str">
         <f>IF(AND($A16="",$C16="",$D16=""),"",IF($A16="","Missing QR Number",IF($C16="","Missing LastName",IF($D16="","Missing FirstName",IF(COUNTIFS($A$3:$A$1000,$A16,$B$3:$B$1000,"Head")=0,"No Head in this family",IF(COUNTIFS($A$3:$A$1000,$A16,$B$3:$B$1000,"Head")&gt;1,"More than one Head","OK"))))))</f>
@@ -3010,149 +2914,147 @@
         <v>36</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>115</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
       <c r="G17" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="J17" s="11"/>
       <c r="K17" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="O17" s="12" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q17" s="12"/>
       <c r="R17" s="12"/>
       <c r="S17" t="str">
         <f>IF(AND($A17="",$C17="",$D17=""),"",IF($A17="","Missing QR Number",IF($C17="","Missing LastName",IF($D17="","Missing FirstName",IF(COUNTIFS($A$3:$A$1000,$A17,$B$3:$B$1000,"Head")=0,"No Head in this family",IF(COUNTIFS($A$3:$A$1000,$A17,$B$3:$B$1000,"Head")&gt;1,"More than one Head","OK"))))))</f>
-        <v>More than one Head</v>
+        <v>Missing LastName</v>
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="11"/>
+      <c r="A18" s="11" t="s">
+        <v>37</v>
+      </c>
       <c r="B18" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
       <c r="G18" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="J18" s="11"/>
+        <v>174</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>87</v>
+      </c>
       <c r="K18" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Q18" s="12"/>
       <c r="R18" s="12"/>
       <c r="S18" t="str">
         <f>IF(AND($A18="",$C18="",$D18=""),"",IF($A18="","Missing QR Number",IF($C18="","Missing LastName",IF($D18="","Missing FirstName",IF(COUNTIFS($A$3:$A$1000,$A18,$B$3:$B$1000,"Head")=0,"No Head in this family",IF(COUNTIFS($A$3:$A$1000,$A18,$B$3:$B$1000,"Head")&gt;1,"More than one Head","OK"))))))</f>
-        <v>Missing QR Number</v>
+        <v>More than one Head</v>
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="11" t="s">
-        <v>37</v>
-      </c>
+      <c r="A19" s="11"/>
       <c r="B19" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
       <c r="G19" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J19" s="11"/>
       <c r="K19" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="O19" s="12" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="P19" s="12" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q19" s="12"/>
       <c r="R19" s="12"/>
       <c r="S19" t="str">
         <f>IF(AND($A19="",$C19="",$D19=""),"",IF($A19="","Missing QR Number",IF($C19="","Missing LastName",IF($D19="","Missing FirstName",IF(COUNTIFS($A$3:$A$1000,$A19,$B$3:$B$1000,"Head")=0,"No Head in this family",IF(COUNTIFS($A$3:$A$1000,$A19,$B$3:$B$1000,"Head")&gt;1,"More than one Head","OK"))))))</f>
-        <v>More than one Head</v>
+        <v>Missing QR Number</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3160,43 +3062,43 @@
         <v>38</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
       <c r="G20" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J20" s="11"/>
       <c r="K20" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q20" s="12"/>
       <c r="R20" s="12"/>
@@ -3210,43 +3112,43 @@
         <v>39</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
       <c r="G21" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J21" s="11"/>
       <c r="K21" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
@@ -3260,155 +3162,149 @@
         <v>40</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
       <c r="G22" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J22" s="11"/>
       <c r="K22" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="O22" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q22" s="12"/>
       <c r="R22" s="12"/>
-      <c r="S22" t="e">
+      <c r="S22" t="str">
         <f>IF(AND($A22="",$C22="",$D22=""),"",IF($A22="","Missing QR Number",IF($C22="","Missing LastName",IF($D22="","Missing FirstName",IF(COUNTIFS($A$3:$A$1000,$A22,$B$3:$B$1000,"Head")=0,"No Head in this family",IF(COUNTIFS($A$3:$A$1000,$A22,$B$3:$B$1000,"Head")&gt;1,"More than one Head","OK"))))))</f>
-        <v>#REF!</v>
+        <v>More than one Head</v>
       </c>
     </row>
     <row r="23" spans="1:19">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="11" t="s">
         <v>41</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
       <c r="G23" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q23" s="12"/>
       <c r="R23" s="12"/>
-      <c r="S23" t="str">
+      <c r="S23" t="e">
         <f>IF(AND($A23="",$C23="",$D23=""),"",IF($A23="","Missing QR Number",IF($C23="","Missing LastName",IF($D23="","Missing FirstName",IF(COUNTIFS($A$3:$A$1000,$A23,$B$3:$B$1000,"Head")=0,"No Head in this family",IF(COUNTIFS($A$3:$A$1000,$A23,$B$3:$B$1000,"Head")&gt;1,"More than one Head","OK"))))))</f>
-        <v>OK</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>167</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
       <c r="G24" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>95</v>
+        <v>171</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>86</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="J24" s="11"/>
       <c r="K24" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q24" s="12"/>
       <c r="R24" s="12"/>
       <c r="S24" t="str">
         <f>IF(AND($A24="",$C24="",$D24=""),"",IF($A24="","Missing QR Number",IF($C24="","Missing LastName",IF($D24="","Missing FirstName",IF(COUNTIFS($A$3:$A$1000,$A24,$B$3:$B$1000,"Head")=0,"No Head in this family",IF(COUNTIFS($A$3:$A$1000,$A24,$B$3:$B$1000,"Head")&gt;1,"More than one Head","OK"))))))</f>
-        <v>More than one Head</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3416,47 +3312,49 @@
         <v>43</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="F25" s="12"/>
+        <v>108</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>170</v>
+      </c>
       <c r="G25" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q25" s="12"/>
       <c r="R25" s="12"/>
@@ -3467,35 +3365,51 @@
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="I26" s="12"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
+        <v>97</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>233</v>
+      </c>
       <c r="Q26" s="12"/>
       <c r="R26" s="12"/>
       <c r="S26" t="str">
@@ -3505,26 +3419,26 @@
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="11"/>
@@ -3546,48 +3460,32 @@
         <v>44</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="K28" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="M28" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="N28" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="O28" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="P28" s="12" t="s">
-        <v>230</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="I28" s="12"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="12"/>
       <c r="Q28" s="12"/>
       <c r="R28" s="12"/>
       <c r="S28" t="str">
@@ -3600,47 +3498,47 @@
         <v>45</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q29" s="12"/>
       <c r="R29" s="12"/>
@@ -3651,35 +3549,51 @@
     </row>
     <row r="30" spans="1:19">
       <c r="A30" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="I30" s="12"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
+        <v>171</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="M30" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="O30" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="P30" s="12" t="s">
+        <v>235</v>
+      </c>
       <c r="Q30" s="12"/>
       <c r="R30" s="12"/>
       <c r="S30" t="str">
@@ -3689,51 +3603,35 @@
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>126</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="M31" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="N31" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="O31" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="P31" s="12" t="s">
-        <v>221</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="I31" s="12"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
       <c r="Q31" s="12"/>
       <c r="R31" s="12"/>
       <c r="S31" t="str">
@@ -3742,50 +3640,80 @@
       </c>
     </row>
     <row r="32" spans="1:19">
-      <c r="A32" s="11"/>
+      <c r="A32" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="B32" s="12" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="I32" s="12"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12"/>
+        <v>97</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="M32" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="O32" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="P32" s="12" t="s">
+        <v>225</v>
+      </c>
       <c r="Q32" s="12"/>
       <c r="R32" s="12"/>
       <c r="S32" t="str">
         <f>IF(AND($A32="",$C32="",$D32=""),"",IF($A32="","Missing QR Number",IF($C32="","Missing LastName",IF($D32="","Missing FirstName",IF(COUNTIFS($A$3:$A$1000,$A32,$B$3:$B$1000,"Head")=0,"No Head in this family",IF(COUNTIFS($A$3:$A$1000,$A32,$B$3:$B$1000,"Head")&gt;1,"More than one Head","OK"))))))</f>
-        <v>Missing QR Number</v>
+        <v>More than one Head</v>
       </c>
     </row>
     <row r="33" spans="1:19">
       <c r="A33" s="11"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
+      <c r="B33" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>162</v>
+      </c>
       <c r="F33" s="12"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="12"/>
+      <c r="G33" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="I33" s="12"/>
       <c r="J33" s="11"/>
       <c r="K33" s="12"/>
@@ -3798,7 +3726,7 @@
       <c r="R33" s="12"/>
       <c r="S33" t="str">
         <f>IF(AND($A33="",$C33="",$D33=""),"",IF($A33="","Missing QR Number",IF($C33="","Missing LastName",IF($D33="","Missing FirstName",IF(COUNTIFS($A$3:$A$1000,$A33,$B$3:$B$1000,"Head")=0,"No Head in this family",IF(COUNTIFS($A$3:$A$1000,$A33,$B$3:$B$1000,"Head")&gt;1,"More than one Head","OK"))))))</f>
-        <v/>
+        <v>Missing QR Number</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -27017,7 +26945,7 @@
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="Q1:Q1"/>
     <mergeCell ref="R1:R1"/>
-    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A32:A33"/>
   </mergeCells>
   <conditionalFormatting sqref="S3:S1000">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -27057,13 +26985,13 @@
     <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Pick a value from the dropdown list." sqref="N3:N1000">
       <formula1>Reference!$H$2:$H$12</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Pick a value from the dropdown list." promptTitle="Barangay" prompt="Head: pick the barangay. Members: leave blank — they use the head's." sqref="P3:P1000">
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Pick a value from the dropdown list." promptTitle="Barangay" prompt="Head: pick the barangay. Members: leave blank - they use the head's." sqref="P3:P1000">
       <formula1>Reference!$I$2:$I$25</formula1>
     </dataValidation>
     <dataValidation type="none" errorStyle="stop" operator="between" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="0" promptTitle="QR Number" prompt="Same number for everyone in one family." sqref="A3:A1000"/>
     <dataValidation type="none" errorStyle="stop" operator="between" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="0" promptTitle="Birthday" prompt="Format: MM-DD-YYYY (e.g. 05-14-1980)." sqref="G3:G1000"/>
     <dataValidation type="none" errorStyle="stop" operator="between" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="0" promptTitle="ContactNumber" prompt="11 digits, e.g. 09171234567." sqref="J3:J1000"/>
-    <dataValidation type="none" errorStyle="stop" operator="between" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="0" promptTitle="Address" prompt="Head: full house/street address. Members: leave blank — they use the head's address." sqref="O3:O1000"/>
+    <dataValidation type="none" errorStyle="stop" operator="between" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="0" promptTitle="Address" prompt="Head: full house/street address. Members: leave blank - they use the head's address." sqref="O3:O1000"/>
     <dataValidation type="none" errorStyle="stop" operator="between" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="0" promptTitle="Sector" prompt="WHO they are. Sector code(s), comma-separated: SC, PWD, SP, B, LGBT, OFW, IP, IDP, PDL. Use OTHER if none apply. See Reference." sqref="Q3:Q1000"/>
     <dataValidation type="none" errorStyle="stop" operator="between" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="0" promptTitle="Services" prompt="Programs RECEIVED. Service code(s), comma-separated (e.g. SC1, FA6, 4PS, EDA5). See Reference." sqref="R3:R1000"/>
   </dataValidations>
@@ -27080,7 +27008,7 @@
     <tabColor rgb="FF2E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="16.425" bestFit="true" customWidth="true" style="0"/>
@@ -27091,7 +27019,7 @@
     <col min="6" max="6" width="28.136" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="23.423" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="25.851" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="16.425" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="9.10" bestFit="true" style="0"/>
     <col min="11" max="11" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="12" max="12" width="32.992" bestFit="true" customWidth="true" style="0"/>
@@ -27103,431 +27031,431 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>301</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>256</v>
       </c>
       <c r="D2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>266</v>
       </c>
       <c r="F2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="G2" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="H2" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I2" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="K2" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="L2" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="N2" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
       <c r="O2" t="s">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="P2" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>238</v>
       </c>
       <c r="B3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>257</v>
       </c>
       <c r="D3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>267</v>
       </c>
       <c r="F3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G3" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="H3" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="I3" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="K3" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="L3" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="N3" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="O3" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="P3" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>239</v>
       </c>
       <c r="B4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D4" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="F4" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G4" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="H4" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="I4" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="K4" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="L4" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="N4" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="O4" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="P4" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D5" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E5" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="F5" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="G5" t="s">
-        <v>177</v>
+        <v>289</v>
       </c>
       <c r="H5" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="I5" t="s">
-        <v>219</v>
+        <v>317</v>
       </c>
       <c r="K5" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="L5" t="s">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="N5" t="s">
+        <v>369</v>
+      </c>
+      <c r="O5" t="s">
+        <v>370</v>
+      </c>
+      <c r="P5" t="s">
         <v>341</v>
-      </c>
-      <c r="O5" t="s">
-        <v>342</v>
-      </c>
-      <c r="P5" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B6" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E6" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="F6" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="G6" t="s">
-        <v>178</v>
+        <v>290</v>
       </c>
       <c r="H6" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="I6" t="s">
-        <v>102</v>
+        <v>318</v>
       </c>
       <c r="K6" t="s">
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="L6" t="s">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="N6" t="s">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="O6" t="s">
-        <v>345</v>
+        <v>372</v>
       </c>
       <c r="P6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B7" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D7" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E7" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="F7" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="G7" t="s">
-        <v>181</v>
+        <v>291</v>
       </c>
       <c r="H7" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="I7" t="s">
-        <v>225</v>
+        <v>319</v>
       </c>
       <c r="K7" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="L7" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="N7" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="O7" t="s">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="P7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B8" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E8" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="F8" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="G8" t="s">
-        <v>180</v>
+        <v>292</v>
       </c>
       <c r="H8" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="I8" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="K8" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="L8" t="s">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="N8" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="O8" t="s">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="P8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E9" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="G9" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="H9" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="I9" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="K9" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="L9" t="s">
-        <v>325</v>
+        <v>354</v>
       </c>
       <c r="N9" t="s">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="O9" t="s">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="P9" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E10" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="G10" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="H10" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="I10" t="s">
-        <v>229</v>
+        <v>322</v>
       </c>
       <c r="K10" t="s">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="L10" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="N10" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="O10" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="P10" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E11" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="G11" t="s">
-        <v>185</v>
+        <v>295</v>
       </c>
       <c r="H11" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="I11" t="s">
-        <v>222</v>
+        <v>323</v>
       </c>
       <c r="K11" t="s">
-        <v>328</v>
+        <v>246</v>
       </c>
       <c r="L11" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="N11" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="O11" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="P11" t="s">
         <v>343</v>
@@ -27535,28 +27463,28 @@
     </row>
     <row r="12" spans="1:16">
       <c r="E12" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="G12" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="H12" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="I12" t="s">
-        <v>223</v>
+        <v>324</v>
       </c>
       <c r="K12" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="L12" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="N12" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="O12" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="P12" t="s">
         <v>343</v>
@@ -27564,19 +27492,19 @@
     </row>
     <row r="13" spans="1:16">
       <c r="E13" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="G13" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="I13" t="s">
-        <v>221</v>
+        <v>325</v>
       </c>
       <c r="N13" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="O13" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="P13" t="s">
         <v>343</v>
@@ -27584,449 +27512,427 @@
     </row>
     <row r="14" spans="1:16">
       <c r="E14" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>298</v>
       </c>
       <c r="I14" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="N14" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="O14" t="s">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="P14" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="G15" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="I15" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="N15" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="O15" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="P15" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="G16" t="s">
-        <v>179</v>
+        <v>300</v>
       </c>
       <c r="I16" t="s">
-        <v>220</v>
+        <v>328</v>
       </c>
       <c r="N16" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="O16" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="P16" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" spans="1:16">
       <c r="G17" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="I17" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="N17" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="O17" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="P17" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:16">
       <c r="I18" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="N18" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="O18" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="P18" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:16">
       <c r="I19" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="N19" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="O19" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="P19" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="I20" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="N20" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="O20" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="P20" t="s">
-        <v>314</v>
+        <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="I21" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="N21" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="O21" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="P21" t="s">
-        <v>314</v>
+        <v>403</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="I22" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="N22" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="O22" t="s">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="P22" t="s">
-        <v>314</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="I23" t="s">
-        <v>224</v>
+        <v>335</v>
       </c>
       <c r="N23" t="s">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="O23" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="P23" t="s">
-        <v>314</v>
+        <v>403</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="I24" t="s">
-        <v>231</v>
+        <v>336</v>
       </c>
       <c r="N24" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="O24" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="P24" t="s">
-        <v>314</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="I25" t="s">
-        <v>226</v>
+        <v>337</v>
       </c>
       <c r="N25" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="O25" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="P25" t="s">
-        <v>312</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="N26" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="O26" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="P26" t="s">
-        <v>312</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="N27" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="O27" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="P27" t="s">
-        <v>312</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="N28" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="O28" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="P28" t="s">
-        <v>312</v>
+        <v>415</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="N29" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="O29" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="P29" t="s">
-        <v>312</v>
+        <v>415</v>
       </c>
     </row>
     <row r="30" spans="1:16">
       <c r="N30" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="O30" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="P30" t="s">
-        <v>312</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" spans="1:16">
       <c r="N31" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="O31" t="s">
-        <v>368</v>
+        <v>423</v>
       </c>
       <c r="P31" t="s">
-        <v>312</v>
+        <v>415</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="N32" t="s">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="O32" t="s">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="P32" t="s">
-        <v>312</v>
+        <v>415</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="N33" t="s">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="O33" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="P33" t="s">
-        <v>312</v>
+        <v>415</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="N34" t="s">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="O34" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="P34" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="N35" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="O35" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="P35" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="N36" t="s">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="O36" t="s">
-        <v>406</v>
+        <v>433</v>
       </c>
       <c r="P36" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="N37" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="O37" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="P37" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="N38" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="O38" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="P38" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
     </row>
     <row r="39" spans="1:16">
       <c r="N39" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="O39" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="P39" t="s">
-        <v>402</v>
+        <v>440</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="N40" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="O40" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="P40" t="s">
-        <v>402</v>
+        <v>440</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="N41" t="s">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="O41" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="P41" t="s">
-        <v>402</v>
+        <v>440</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="N42" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="O42" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="P42" t="s">
-        <v>402</v>
+        <v>440</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="N43" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="O43" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="P43" t="s">
-        <v>402</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44" spans="1:16">
       <c r="N44" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="O44" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="P44" t="s">
-        <v>402</v>
+        <v>440</v>
       </c>
     </row>
     <row r="45" spans="1:16">
       <c r="N45" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="O45" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="P45" t="s">
-        <v>402</v>
+        <v>440</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="N46" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="O46" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="P46" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
     </row>
     <row r="47" spans="1:16">
       <c r="N47" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="O47" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="P47" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="N48" t="s">
-        <v>429</v>
-      </c>
-      <c r="O48" t="s">
-        <v>430</v>
-      </c>
-      <c r="P48" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16">
-      <c r="N49" t="s">
-        <v>431</v>
-      </c>
-      <c r="O49" t="s">
-        <v>432</v>
-      </c>
-      <c r="P49" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -28158,53 +28064,53 @@
         <v>26</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>434</v>
+        <v>112</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>252</v>
+        <v>459</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>273</v>
+        <v>460</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -28212,49 +28118,49 @@
         <v>26</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>434</v>
+        <v>112</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8" t="s">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>252</v>
+        <v>459</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>270</v>
+        <v>466</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>278</v>
+        <v>467</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>284</v>
+        <v>468</v>
       </c>
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
       <c r="Q4" s="8" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>425</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -28262,43 +28168,43 @@
         <v>26</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>434</v>
+        <v>112</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>443</v>
+        <v>470</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8" t="s">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>251</v>
+        <v>472</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
       <c r="L5" s="8" t="s">
-        <v>269</v>
+        <v>473</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>277</v>
+        <v>474</v>
       </c>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="8" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -28306,56 +28212,56 @@
         <v>28</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>251</v>
+        <v>472</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>258</v>
+        <v>477</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>271</v>
+        <v>478</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>449</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:18" customHeight="1" ht="70">
       <c r="A8" s="9" t="s">
-        <v>450</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
